--- a/diseases/d123/2000-2004.xlsx
+++ b/diseases/d123/2000-2004.xlsx
@@ -1567,7 +1567,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN56" t="b">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -15877,7 +15877,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16831,7 +16831,7 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN86" t="b">
@@ -17785,7 +17785,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18739,7 +18739,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -19693,7 +19693,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20647,7 +20647,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN106" t="b">
@@ -21601,7 +21601,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22555,7 +22555,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -23509,7 +23509,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24856,7 +24856,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -25810,7 +25810,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -26764,7 +26764,7 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN138" t="b">
@@ -27718,7 +27718,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -28672,7 +28672,7 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN148" t="b">
@@ -29626,7 +29626,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -30580,7 +30580,7 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN158" t="b">
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -32488,7 +32488,7 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN168" t="b">
@@ -33442,7 +33442,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -34396,7 +34396,7 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN178" t="b">
@@ -35350,7 +35350,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -36697,7 +36697,7 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN190" t="b">
@@ -37651,7 +37651,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -38605,7 +38605,7 @@
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN200" t="b">
@@ -39559,7 +39559,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -40513,7 +40513,7 @@
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN210" t="b">
@@ -41467,7 +41467,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -42421,7 +42421,7 @@
       </c>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN220" t="b">
@@ -43375,7 +43375,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -44329,7 +44329,7 @@
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN230" t="b">
@@ -45283,7 +45283,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -46237,7 +46237,7 @@
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN240" t="b">
@@ -47191,7 +47191,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -48538,7 +48538,7 @@
       </c>
       <c r="AM252" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN252" t="b">
@@ -49492,7 +49492,7 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -50446,7 +50446,7 @@
       </c>
       <c r="AM262" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN262" t="b">
@@ -51400,7 +51400,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -52354,7 +52354,7 @@
       </c>
       <c r="AM272" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN272" t="b">
@@ -53308,7 +53308,7 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN277" t="b">
@@ -54262,7 +54262,7 @@
       </c>
       <c r="AM282" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN282" t="b">
@@ -55216,7 +55216,7 @@
       </c>
       <c r="AM287" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN287" t="b">
@@ -56170,7 +56170,7 @@
       </c>
       <c r="AM292" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN292" t="b">
@@ -57124,7 +57124,7 @@
       </c>
       <c r="AM297" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN297" t="b">
@@ -58078,7 +58078,7 @@
       </c>
       <c r="AM302" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN302" t="b">
@@ -59032,7 +59032,7 @@
       </c>
       <c r="AM307" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN307" t="b">
